--- a/data/relatorio_sentimentos.xlsx
+++ b/data/relatorio_sentimentos.xlsx
@@ -511,42 +511,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8882</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,6 +1174,231 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-24T15:47:36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cac3406bcbd4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bradesco abre 225 vagas de emprego no Brasil com oportunidades em tecnologia, negócios e segurança da informação</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bradesco abre 225 vagas de emprego no Brasil com oportunidades em tecnologia, negócios e segurança da informação&amp;nbsp;&amp;nbsp;JC Concursos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOZTNvejdEODhSOEZiQkxfUTNoQjZQcXZRVlB3UmhvcUJKazlCNk5keUJRSEJGOUI0amhXYjZKaGRpYlFpTHkzVFdkc3hJMFlqelVOQXpLSGZzQ3dIMFpmWTNra2wxYU4yN2Itbmp1SGQxakpnR3RWakZoQzNOLVNTVlMxRnotdUY4eDk2Wk41VkdORUY0azVzUzNfY0ZReF9oM3MwOGc5QnZkUFhZNmx1NVRJbDhaMzVKVDJvMnA4OXh6TnBORFVHM2pRSHo3ZUtlTS03N0QybS1LN0tyQzhudndQR203RU1RdGlwN3VlTE1EeHBq0gH6AUFVX3lxTFBvTHlyWVdybTAwaVloXzlnb2syV3A1M0lTeDd6S3NncmxBeVdRS1Q1RENpRURES1RJemtGdl9iMUxkNlFhM3JkczZLZVhiYi11VXdtbUN6QmxmWFFhMkgzcUdqN3lzbndXX1A5OVdGU21LQmdSb1ZUMUxrZjdiMktTMEFBdVo4VnFGbmY1SHZ3UGxlVkZjZE1qUkxpMUQ1ek9OT2F5NVQxRWNDUU5LUXFfMmpYdjgyb3AxdUs1NENhVHRwWF81aFlXLVNRWWtuSGNOdTZKN1VRRE1CQ1VCRzVDNzNzYVZDWHZlZ2JSUFRCQUJPZFlsaGpUNGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>JC Concursos</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-22T21:36:00+00:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bradesco opens 225 job vacancies in Brazil with opportunities in technology, business and information security. Bradesco opens 225 job vacancies in Brazil with opportunities in technology, business and information security&amp;nbsp;&amp;nbsp;JC Concursos</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-24T15:47:36</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>d83715720261</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bradesco oferece mais de 80 cursos gratuitos com certificado online</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bradesco oferece mais de 80 cursos gratuitos com certificado online&amp;nbsp;&amp;nbsp;Serra Noticiário</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQaFRzVENxeS1RbGx3WDBHZEFtZkJ5NC1KTi13aHc5X25uMGVaLXZ6ekNVUzAwcDBBaDBUblQzN0ptSXZ2U284RzNKTGRPVFczY2VDYUIyX0hUOGpNZTVNYnNjOFZnc0E5ZndjVG5UYnhkV1V2d0dJWmw2bkNSaHhNYjMyM3NPRlFiUkNfbXNoQ0tYVW5laV9hYzhIc2dTb2Fx?oc=5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Serra Noticiário</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-23T18:25:00+00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9221</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bradesco offers more than 80 free courses with online certificates. Bradesco offers more than 80 free courses with online certificate&amp;nbsp;&amp;nbsp;Serra Noticiário</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-24T15:47:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9ae5cbab2aa4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bradesco Seguros divulga ações durante Maio Amarelo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bradesco Seguros divulga ações durante Maio Amarelo&amp;nbsp;&amp;nbsp;Grandes Nomes da Propaganda</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT0ZBekUwdzJoUG9uc3E3Wk4tZ1MtUGFSS0dHc09KYXZrc012SzRNZlprWGl1RF9kUW0ya0lDV1hJbzdWYldsb3pVTU9DMHVmSmhSQURkTzBLd3lhV0VhSGdTLXpfVENmQUtmWkNvYWxfMGozOXdQbDIwUmxRMXFtbkpfbHRNTGxiQ1d0Si1ZbEN5cTBWRmk4ek9nSWQxQVRBbHZPUW5aekd1WkpU?oc=5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Grandes Nomes da Propaganda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-05-23T05:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bradesco Seguros publishes actions during Yellow May. Bradesco Seguros announces actions during Yellow May&amp;nbsp;&amp;nbsp;Big Names in Advertising</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1221,10 +1446,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/relatorio_sentimentos.xlsx
+++ b/data/relatorio_sentimentos.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Histórico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,12 +37,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -438,67 +426,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Notícias</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Positivas</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Negativas</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Neutras</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Inconclusivas</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Confiança Média</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Sentimento Geral</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>% Positivas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>% Negativas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bart_vitorias</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>finbert_vitorias</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pct_concordancia</t>
         </is>
@@ -507,43 +495,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -560,91 +548,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>timestamp_coleta</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fonte</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>data_pub</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>termo_busca</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>sentimento_pt</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>sentimento_en</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confianca</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>score_positive</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>score_negative</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>score_neutral</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>texto_analisado</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>erro</t>
         </is>
@@ -653,61 +641,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>f43a8d1f5648</t>
+          <t>a2f432f4f7e7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BBDC4 - Banco Bradesco - Resultados, Dividendos, Cotação e Indicadores</t>
+          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBDC4 - Banco Bradesco - Resultados, Dividendos, Cotação e Indicadores&amp;nbsp;&amp;nbsp;Investidor10</t>
+          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra&amp;nbsp;&amp;nbsp;Estadão</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1Eenpqb3dobnYyTWppWnFRazg2dk9jX05vaUlnYlRMVG81M1haOTJrY0huSTN2RTFaVjRUdURteW95amNmb3BJVjYxTFZESDR3bWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVENxdTl1SGIyb0VaeU1CT3VyTlRHNGZXdk56Smt3S1pPaXZOTmVFSi12Z295aTZQLUxNYmpFSmNHVFBxOE12ejlOT2VqU1BoR0ZhTTJPVTN3YUVxcFlkVmlDX0xPR2Q0RWQ3bzhuUWlFWFU0U2hxaVBZVHhXTnRPaFplUUtmVm5uMDJlSFJxR0FYM3hMSUJrRzdKN3ktSkg1NnZUekc1VHJfbDZlUkN0Wi1YaWUySlJVZkI5LVl4NDBmdUkwYm9ZMXRDQjFYVUJaamdQZ3llc1haQ1V0akHSAeMBQVVfeXFMTjNnR2lnMFB2NmFoXzBRMEVlWFpHZ3BYamIzbXpVMXpORlZrRVJhdndCQ0lXcjNtVGlDakpSWmlhR1A3SENaSndBRXNFeU85SkV1TEZ5M0MwZVBOWnhsWl9nWmU2Y2k0RXdySVBjZFhfODdGRW9RUGtJRWlwTjVkak9vN1RQaC1Gek1JYVJVRUJTRGVrU0ZlSFYwMktTX29oc19rZFY0M1hfUE1YLUtHTjBhN3hTMlVnRm9SRE51X0VNZlM4QktEZmY0M2h2a2tsSFZnUU1EQ2htcmpUbTBaY05rcWc?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Investidor10</t>
+          <t>Estadão</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-22T07:00:00+00:00</t>
+          <t>2026-06-17T22:39:45+00:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.9479</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -720,69 +708,73 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BBDC4 - Banco Bradesco - Results, Dividends, Prices and Indicators. BBDC4 - Banco Bradesco - Results, Dividends, Prices and Indicators&amp;nbsp;&amp;nbsp;Investor10</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra. Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra&amp;nbsp;&amp;nbsp;Estadão</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>321c80649817</t>
+          <t>8437c62dc702</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BBAS3, BBDC4 e ITUB4 perdem força e bancos entram em zona decisiva na Bolsa</t>
+          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBAS3, BBDC4 e ITUB4 perdem força e bancos entram em zona decisiva na Bolsa&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
+          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPWUtWaUlKZ1diU1J3S01nOVhod0ZJUWpLR3RuT0hFXzdCUTNWX0MyaE1fdmhjajhZejBCRVVFcnlEMnVTTGQzd0lqUGwzY2lGQWFtXzN1WXBWdEp0aUhNYl9ZOVVtS3ROWElkLTBfUWlJOEFqUlUyMzd4RGNudUMxcWlCdkk4WXV0elhuZkM4SHlDZVRwUW9ndHpOU3JuMnhKWDJnUEYwZjN3MkNBNHBUbjBOS1N5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPczBJd2hKQ2RwOHVlZzNNbTBFakJSMGNyalEtTFRQSnZYaThuUEcwdzFNWVJoMlBLUkgzQVRIRHEwSlpzay1paE02MzhhWVdfUUd0alR6RVRURnBUUHpBdS05ZDgzbXJPUmk1SHRyd0lDWFBvdnBKazZJaFczWTRNX0xOdDlFUmhTN3RKZ0EyMzVsbXlSZ1Exc1Nn?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Guia do Investidor</t>
+          <t>arevista.com.br</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-22T20:46:21+00:00</t>
+          <t>2026-06-19T16:30:29+00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NEGATIVO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.9445</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -795,69 +787,73 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BBAS3, BBDC4 and ITUB4 lose strength and banks enter a decisive zone on the Stock Exchange. BBAS3, BBDC4 and ITUB4 lose strength and banks enter a decisive zone on the Stock Exchange&amp;nbsp;&amp;nbsp;Investor Guide</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO. PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>467a393c7278</t>
+          <t>93e511b82050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bancos vão cair mais? BBAS3, BBDC4 e ITUB4 acendem alerta no gráfico</t>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bancos vão cair mais? BBAS3, BBDC4 e ITUB4 acendem alerta no gráfico&amp;nbsp;&amp;nbsp;InfoMoney</t>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQY0otSk40UU1uSVljSWplMXRwUFlEZnRpZ3BnSW1JcjBnMlNzSGx5TzUxbmh1TW5MbE5ZcXNuZEtjYi13U1VienZ2NGVlbFRrV2NxU2ZFNnBUX25jRmJhbm81X3ljeFJidl9HRVFFTUs5VkN0T2M1Z1YtZmpma1lNN1JraXZXRDZVYnJKeUxFNWFJS1d0ckNFbU1UOFhORG5BVzZNVE9SMErSAa4BQVVfeXFMUHNjWEVqQVZJaVEzb2RtbnV4bEE3YWlCclRVM0pCazRUVGxZZ1B4TnhmRzVSRlViNW1leFVIZzRrV1lDODE2UUdDOVJ0b2p3aV9TT0NHNzNqMnp2V2V3dWxhTEY0Y3puaDRRc212bVRVWDVqR29nTlF1RFZIU0pycnJqMjAzNlRncE1WRjNuWm9qT0EwdkJjcGd4OVhFeWkzdmg5UmpoNUZrZjdmZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41WDkwUmlQeVRGYjNkLW5Lc3FpMFFUeVFxWVpCcjN2T0FXb0o4bEdBaDdTLTFTVjRkVnZKWFpFQ1FkUkFtaXFmbG12TTFldWczZ25JcW53N1A0M0U0MHRpZU0wS3lENzAzMW5VaGh6Y00?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>InfoMoney</t>
+          <t>tradenews.com.br</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-22T12:42:35+00:00</t>
+          <t>2026-06-18T18:01:39+00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7461</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -870,69 +866,73 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Will banks fall further? BBAS3, BBDC4 and ITUB4 light up an alert on the graph. Will banks fall further? BBAS3, BBDC4 and ITUB4 light up alert on the chart&amp;nbsp;&amp;nbsp;InfoMoney</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso. Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06b561848f57</t>
+          <t>6501afb16592</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4) entra na briga pelos ultrarricos com financiamento de jatos executivos</t>
+          <t>PASS3 projeta valorização superior a 50% com recomendações de compra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4) entra na briga pelos ultrarricos com financiamento de jatos executivos&amp;nbsp;&amp;nbsp;Investidor10</t>
+          <t>PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTHdLU2xMbDZNSkpwOVJtejVhSWhFaXRhM01mdVpMMmJSVWQ4TUlDc25fRWRxUzJ5V09BZE1qM3N0TDdGZmczb3FubWlpYkdZckhmNWpmbWZxSXRDMVBLdWNwMGI2aHhTV3g0VmRJWHFqdHh6d3YwdnR1LUl6VWU4WHZrSGxldlpwUmZobWEtZDZpYXZfQk5wY3Zwak1ySWYzS3o5Qnc4eHBrRlBZN0pyV3J1RnNyOS1sQVBOSU9ZT3pJMFlvUkRUU0F30gHPAUFVX3lxTE03TGo4ek1pQkxjVjdJZUV4X2ktVWRtXzZzaklrZXczOG81N3Z4OFJkRHlkeWdsdDMwZ09uRUZ3RHZkNlVnb05tRTE4OGFnbDJQRzh0c2VfRHNlSk04eHhqSk45Q3VVbVFvV2RuNk5KbXNFNXd3Q0pOUGhJbjJDdnY5UTluT05SSmxqSmF3VjA0R21JdVZLc2RuNnpsa0s4TFZFNW1NZmFnbDR0OXdZSW5TYTI2UVExMGlpaHBJNkNFaUZ1ZlFjczF4ckVjcnRRWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPeXpHT21BQjJxLTlMeGhGQVF0WHRSMHpVanhJTFRuVE9Zdk9VeGtPZlV5TmZoRFp1Z185WDY3dWZ2X1ZxY2FYejllRGVwY3VWaWNOZzN4eTJYc3dPcm9teGVMOVl0dGJaczNVLWZaejJhR3dKU2V2cXVVU3dLdFhUQWNTcTlfa0Jab2I5S2F6OU9KbjFMVXIySw?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Investidor10</t>
+          <t>Acionista.com.br</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-22T13:03:00+00:00</t>
+          <t>2026-06-18T10:44:36+00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>POSITIVO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8957000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -945,69 +945,73 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4) enters the fight for the ultra-rich with financing for executive jets. Bradesco (BBDC4) enters the fight for the ultra-rich with financing for executive jets&amp;nbsp;&amp;nbsp;Investor10</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>PASS3 projeta valorização superior a 50% com recomendações de compra. PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ab8464242ba6</t>
+          <t>15a530bd9989</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4), Copel (CPLE3), Kepler Weber (KEPL3) e outros destaques desta sexta-feira (22)</t>
+          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4), Copel (CPLE3), Kepler Weber (KEPL3) e outros destaques desta sexta-feira (22)&amp;nbsp;&amp;nbsp;Money Times</t>
+          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMUZBNWNFdElZMFZRbUNJcU8wUHRPczh6Vmg1dDY2WVlkUnJWdkFhcE52SE9WZ2NRTzNpR2xOOHB2ZzJSQkNzOS1BekgwZ2RHd3lqRXpaRHhaVU4tNWFsR2hBQ3pwODNXX2VIS2dMNHEyLUF2RHFJc2d0Y1UtQUdqQUd4VjA1MEtxX1daTm5Kdlh3ZGpnT2Q3cFItMTF6WUE0Y2IwTUtSQk11WnJKLXZpREJqV1pwUG9NMTdJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPY2hTVGduakFZNUZxamFhcWFXUFZZUm5JSkVwQW5ESmRkSkhnRTkwNWItelJrbmt0a09DUmFBTEZnNllZTHVZaHVkNXo3RHN5clduQi1zUFI5M19Sby1FeHIwUVlSa3pUbTlfa0prMUJ4ZFhfclBOUy16cF9FV0xxbjJSaHlmVmkyYWdYTjd6TDhvTGdlN1FZZ1JVOGJsRjJ5NjlKVk5uekdNS0hzeVVyd3YzRQ?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Money Times</t>
+          <t>Guia do Investidor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-22T12:57:00+00:00</t>
+          <t>2026-06-18T15:21:11+00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1020,69 +1024,73 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bradesco (BBDC4), Copel (CPLE3), Kepler Weber (KEPL3) and other highlights from this Friday (22). Bradesco (BBDC4), Copel (CPLE3), Kepler Weber (KEPL3) and other highlights from this Friday (22)&amp;nbsp;&amp;nbsp;Money Times</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado. Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5f9686b22311</t>
+          <t>0da4ad0ad7a2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BBDC4, CPLE3 e KEPL3: destaques desta sexta</t>
+          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBDC4, CPLE3 e KEPL3: destaques desta sexta&amp;nbsp;&amp;nbsp;SpaceMoney</t>
+          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPQnZnWGppT2Q0Qk52cHFVS1ZobHlNdXZjWXByMWhJQVQ5ZG5qSXFlTFhGbkdMRUNDRzlOb2VBUmNJLWFpSk5Va1BRRzZwWnFPX3VsZ181dmdreVJhN1FBQVliWTVXMU9adThhQVBsaXIzdHlqMU5xTGhabEN0TzNUMVVuZkt0R1M4ZWt4Um1UemYxWnNmdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE03RElkdzFzcUI2bl8wdkdLaVRveHhqMFlpb1ZlU3M1YVo0c29NMnQwZGRaRGZ0MTVmSno1eVlYbFpKVjdpd0liVUFpckc1NWRpemNjWDZDczRKZzBKQjVfMnVOMEdKMTVhMzhKaDhEN3hXOGVyYjdfaWd6NmtpbDg?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SpaceMoney</t>
+          <t>Acionista.com.br</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-22T14:00:47+00:00</t>
+          <t>2026-06-18T17:42:20+00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.922</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1095,69 +1103,73 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BBDC4, CPLE3 and KEPL3: highlights from this Friday. BBDC4, CPLE3 and KEPL3: highlights this Friday&amp;nbsp;&amp;nbsp;SpaceMoney</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%. PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23T11:21:50</t>
+          <t>2026-06-19T19:03:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>a315e90c8b09</t>
+          <t>dcd8cc10981b</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Com seguro de vida ‘bombando’ e Brasil envelhecendo, Bradesco faz mudança para surfar ‘economia prateada’</t>
+          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Com seguro de vida ‘bombando’ e Brasil envelhecendo, Bradesco faz mudança para surfar ‘economia prateada’&amp;nbsp;&amp;nbsp;O GLOBO</t>
+          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOd29yaGtZNkpDRHlQUkJRN2NoM2pHeGNXTjk5aW16WEZRU0pDUmdpT0VPZElRdmtkbElzTjJXcFQtNC1WSHNVODZLMmpXTGFsR1d3dmk5Vi1GNW1hMFhhYUMyUnliTE5OSHNSUDNZRElJVEViS1pLbzN0NndLSzQzcElfLW1YSTQ5aFpXbHdER1lUdmlXX2dvc3V6cXI2SWJURzlfbXVLTWc2Rk9mSlAyV3ZrYmtIZkVzNlgta0I2UlYxX0doNlFfQVJiVFNLcFM3MnpkSkVldVdQU0JmdWJOTlFIQ0JkOGdjR0JHeDRvMNIB_gFBVV95cUxQWElERGhvemtLYVVfTTJOZWljM2xZSk9taUJZc3hrWThsUDB6b2g4akZuQXZLY0NrcE9LcFZaOTJvckFBS1dxM3YxX29ORW5sUlVjRkNHQXUxMkRyNjJSRFJhVWpUS01NaVdMMUk1cjZvNi12NUhjaGIwcExpbGRpU0hleHhXN0t5NlNNaHY0eGI3ZTgtdjQzRS05cXg3OENadHNia0t3UTNCUWMtTWVjSHNrTi1SenNUR3EwakV4UDVnRXczM0RnN0ZlNHotSWhYMEJMWndWU1gyN19GTGF6aFprRFIxbkptWE8xUDAtUTJYZmJqaUMxUUMta0lQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUmlwQU1FbFMyUTBfa1VTVG9fMkVFMlRGdXNqaW1kbnVqTjNhMmx6M1o5SHdwQV9FejBFWHp0eThoTC1pMVNVaHNCeVBaZlJBTkRTbDhmc19uNG9iQVItSXBmQUtQUFNvUnQ4Y19QNU92SnllR0Vmd0VMM2p2RUJORU9PRHpubXRYWEtTX2lNMkh1dGJWUEc2RUtYRHptVGdJQnZMS3V1T0dGdw?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>O GLOBO</t>
+          <t>Money Times</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-21T15:56:10+00:00</t>
+          <t>2026-06-18T15:21:00+00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bradesco</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>POSITIVO</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.8179</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1170,235 +1182,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>With life insurance ‘booming’ and Brazil aging, Bradesco makes changes to surf the ‘silver economy’. With life insurance ‘booming’ and Brazil aging, Bradesco makes change to surf the ‘silver economy’&amp;nbsp;&amp;nbsp;O GLOBO</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-24T15:47:36</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BBDC4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cac3406bcbd4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bradesco abre 225 vagas de emprego no Brasil com oportunidades em tecnologia, negócios e segurança da informação</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bradesco abre 225 vagas de emprego no Brasil com oportunidades em tecnologia, negócios e segurança da informação&amp;nbsp;&amp;nbsp;JC Concursos</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOZTNvejdEODhSOEZiQkxfUTNoQjZQcXZRVlB3UmhvcUJKazlCNk5keUJRSEJGOUI0amhXYjZKaGRpYlFpTHkzVFdkc3hJMFlqelVOQXpLSGZzQ3dIMFpmWTNra2wxYU4yN2Itbmp1SGQxakpnR3RWakZoQzNOLVNTVlMxRnotdUY4eDk2Wk41VkdORUY0azVzUzNfY0ZReF9oM3MwOGc5QnZkUFhZNmx1NVRJbDhaMzVKVDJvMnA4OXh6TnBORFVHM2pRSHo3ZUtlTS03N0QybS1LN0tyQzhudndQR203RU1RdGlwN3VlTE1EeHBq0gH6AUFVX3lxTFBvTHlyWVdybTAwaVloXzlnb2syV3A1M0lTeDd6S3NncmxBeVdRS1Q1RENpRURES1RJemtGdl9iMUxkNlFhM3JkczZLZVhiYi11VXdtbUN6QmxmWFFhMkgzcUdqN3lzbndXX1A5OVdGU21LQmdSb1ZUMUxrZjdiMktTMEFBdVo4VnFGbmY1SHZ3UGxlVkZjZE1qUkxpMUQ1ek9OT2F5NVQxRWNDUU5LUXFfMmpYdjgyb3AxdUs1NENhVHRwWF81aFlXLVNRWWtuSGNOdTZKN1VRRE1CQ1VCRzVDNzNzYVZDWHZlZ2JSUFRCQUJPZFlsaGpUNGc?oc=5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>JC Concursos</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-05-22T21:36:00+00:00</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Bradesco</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>POSITIVO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bradesco opens 225 job vacancies in Brazil with opportunities in technology, business and information security. Bradesco opens 225 job vacancies in Brazil with opportunities in technology, business and information security&amp;nbsp;&amp;nbsp;JC Concursos</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-05-24T15:47:36</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BBDC4</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>d83715720261</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bradesco oferece mais de 80 cursos gratuitos com certificado online</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bradesco oferece mais de 80 cursos gratuitos com certificado online&amp;nbsp;&amp;nbsp;Serra Noticiário</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQaFRzVENxeS1RbGx3WDBHZEFtZkJ5NC1KTi13aHc5X25uMGVaLXZ6ekNVUzAwcDBBaDBUblQzN0ptSXZ2U284RzNKTGRPVFczY2VDYUIyX0hUOGpNZTVNYnNjOFZnc0E5ZndjVG5UYnhkV1V2d0dJWmw2bkNSaHhNYjMyM3NPRlFiUkNfbXNoQ0tYVW5laV9hYzhIc2dTb2Fx?oc=5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Serra Noticiário</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-05-23T18:25:00+00:00</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Bradesco</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.9221</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bradesco offers more than 80 free courses with online certificates. Bradesco offers more than 80 free courses with online certificate&amp;nbsp;&amp;nbsp;Serra Noticiário</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-05-24T15:47:36</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BBDC4</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9ae5cbab2aa4</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bradesco Seguros divulga ações durante Maio Amarelo</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bradesco Seguros divulga ações durante Maio Amarelo&amp;nbsp;&amp;nbsp;Grandes Nomes da Propaganda</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT0ZBekUwdzJoUG9uc3E3Wk4tZ1MtUGFSS0dHc09KYXZrc012SzRNZlprWGl1RF9kUW0ya0lDV1hJbzdWYldsb3pVTU9DMHVmSmhSQURkTzBLd3lhV0VhSGdTLXpfVENmQUtmWkNvYWxfMGozOXdQbDIwUmxRMXFtbkpfbHRNTGxiQ1d0Si1ZbEN5cTBWRmk4ek9nSWQxQVRBbHZPUW5aekd1WkpU?oc=5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Grandes Nomes da Propaganda</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-05-23T05:01:00+00:00</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bradesco</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bradesco Seguros publishes actions during Yellow May. Bradesco Seguros announces actions during Yellow May&amp;nbsp;&amp;nbsp;Big Names in Advertising</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?. Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>No module named 'transformers'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1411,45 +1202,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>NEGATIVO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>POSITIVO</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INCONCLUSIVO</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>BBDC4</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/relatorio_sentimentos.xlsx
+++ b/data/relatorio_sentimentos.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -651,32 +651,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a2f432f4f7e7</t>
+          <t>8437c62dc702</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra</t>
+          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra&amp;nbsp;&amp;nbsp;Estadão</t>
+          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVENxdTl1SGIyb0VaeU1CT3VyTlRHNGZXdk56Smt3S1pPaXZOTmVFSi12Z295aTZQLUxNYmpFSmNHVFBxOE12ejlOT2VqU1BoR0ZhTTJPVTN3YUVxcFlkVmlDX0xPR2Q0RWQ3bzhuUWlFWFU0U2hxaVBZVHhXTnRPaFplUUtmVm5uMDJlSFJxR0FYM3hMSUJrRzdKN3ktSkg1NnZUekc1VHJfbDZlUkN0Wi1YaWUySlJVZkI5LVl4NDBmdUkwYm9ZMXRDQjFYVUJaamdQZ3llc1haQ1V0akHSAeMBQVVfeXFMTjNnR2lnMFB2NmFoXzBRMEVlWFpHZ3BYamIzbXpVMXpORlZrRVJhdndCQ0lXcjNtVGlDakpSWmlhR1A3SENaSndBRXNFeU85SkV1TEZ5M0MwZVBOWnhsWl9nWmU2Y2k0RXdySVBjZFhfODdGRW9RUGtJRWlwTjVkak9vN1RQaC1Gek1JYVJVRUJTRGVrU0ZlSFYwMktTX29oc19rZFY0M1hfUE1YLUtHTjBhN3hTMlVnRm9SRE51X0VNZlM4QktEZmY0M2h2a2tsSFZnUU1EQ2htcmpUbTBaY05rcWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPczBJd2hKQ2RwOHVlZzNNbTBFakJSMGNyalEtTFRQSnZYaThuUEcwdzFNWVJoMlBLUkgzQVRIRHEwSlpzay1paE02MzhhWVdfUUd0alR6RVRURnBUUHpBdS05ZDgzbXJPUmk1SHRyd0lDWFBvdnBKazZJaFczWTRNX0xOdDlFUmhTN3RKZ0EyMzVsbXlSZ1Exc1Nn?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Estadão</t>
+          <t>arevista.com.br</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-17T22:39:45+00:00</t>
+          <t>2026-06-19T16:30:29+00:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,19 +708,19 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra. Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra&amp;nbsp;&amp;nbsp;Estadão</t>
+          <t>PASS3 gains endorsement from large banks and could rise up to 52% after IPO. PASS3 gains endorsement from large banks and could rise up to 52% after IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -730,32 +730,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8437c62dc702</t>
+          <t>93e511b82050</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO</t>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPczBJd2hKQ2RwOHVlZzNNbTBFakJSMGNyalEtTFRQSnZYaThuUEcwdzFNWVJoMlBLUkgzQVRIRHEwSlpzay1paE02MzhhWVdfUUd0alR6RVRURnBUUHpBdS05ZDgzbXJPUmk1SHRyd0lDWFBvdnBKazZJaFczWTRNX0xOdDlFUmhTN3RKZ0EyMzVsbXlSZ1Exc1Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41WDkwUmlQeVRGYjNkLW5Lc3FpMFFUeVFxWVpCcjN2T0FXb0o4bEdBaDdTLTFTVjRkVnZKWFpFQ1FkUkFtaXFmbG12TTFldWczZ25JcW53N1A0M0U0MHRpZU0wS3lENzAzMW5VaGh6Y00?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>arevista.com.br</t>
+          <t>tradenews.com.br</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19T16:30:29+00:00</t>
+          <t>2026-06-18T18:01:39+00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -787,19 +787,19 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO. PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
+          <t>Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario. Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,32 +809,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>93e511b82050</t>
+          <t>6501afb16592</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso</t>
+          <t>PASS3 projeta valorização superior a 50% com recomendações de compra</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
+          <t>PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41WDkwUmlQeVRGYjNkLW5Lc3FpMFFUeVFxWVpCcjN2T0FXb0o4bEdBaDdTLTFTVjRkVnZKWFpFQ1FkUkFtaXFmbG12TTFldWczZ25JcW53N1A0M0U0MHRpZU0wS3lENzAzMW5VaGh6Y00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPeXpHT21BQjJxLTlMeGhGQVF0WHRSMHpVanhJTFRuVE9Zdk9VeGtPZlV5TmZoRFp1Z185WDY3dWZ2X1ZxY2FYejllRGVwY3VWaWNOZzN4eTJYc3dPcm9teGVMOVl0dGJaczNVLWZaejJhR3dKU2V2cXVVU3dLdFhUQWNTcTlfa0Jab2I5S2F6OU9KbjFMVXIySw?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tradenews.com.br</t>
+          <t>Acionista.com.br</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-18T18:01:39+00:00</t>
+          <t>2026-06-18T10:44:36+00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso. Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
+          <t>PASS3 projects appreciation of more than 50% with purchase recommendations. PASS3 projects appreciation of more than 50% with purchase recommendations&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -888,32 +888,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6501afb16592</t>
+          <t>15a530bd9989</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PASS3 projeta valorização superior a 50% com recomendações de compra</t>
+          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPeXpHT21BQjJxLTlMeGhGQVF0WHRSMHpVanhJTFRuVE9Zdk9VeGtPZlV5TmZoRFp1Z185WDY3dWZ2X1ZxY2FYejllRGVwY3VWaWNOZzN4eTJYc3dPcm9teGVMOVl0dGJaczNVLWZaejJhR3dKU2V2cXVVU3dLdFhUQWNTcTlfa0Jab2I5S2F6OU9KbjFMVXIySw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPY2hTVGduakFZNUZxamFhcWFXUFZZUm5JSkVwQW5ESmRkSkhnRTkwNWItelJrbmt0a09DUmFBTEZnNllZTHVZaHVkNXo3RHN5clduQi1zUFI5M19Sby1FeHIwUVlSa3pUbTlfa0prMUJ4ZFhfclBOUy16cF9FV0xxbjJSaHlmVmkyYWdYTjd6TDhvTGdlN1FZZ1JVOGJsRjJ5NjlKVk5uekdNS0hzeVVyd3YzRQ?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acionista.com.br</t>
+          <t>Guia do Investidor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-18T10:44:36+00:00</t>
+          <t>2026-06-18T15:21:11+00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -945,19 +945,19 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PASS3 projeta valorização superior a 50% com recomendações de compra. PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Compass (PASS3): five banks see an increase of up to 49% and point out a market error. Compass (PASS3): five banks see an increase of up to 49% and point out market error&amp;nbsp;&amp;nbsp;Investor Guide</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -967,32 +967,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15a530bd9989</t>
+          <t>0da4ad0ad7a2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado</t>
+          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
+          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPY2hTVGduakFZNUZxamFhcWFXUFZZUm5JSkVwQW5ESmRkSkhnRTkwNWItelJrbmt0a09DUmFBTEZnNllZTHVZaHVkNXo3RHN5clduQi1zUFI5M19Sby1FeHIwUVlSa3pUbTlfa0prMUJ4ZFhfclBOUy16cF9FV0xxbjJSaHlmVmkyYWdYTjd6TDhvTGdlN1FZZ1JVOGJsRjJ5NjlKVk5uekdNS0hzeVVyd3YzRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE03RElkdzFzcUI2bl8wdkdLaVRveHhqMFlpb1ZlU3M1YVo0c29NMnQwZGRaRGZ0MTVmSno1eVlYbFpKVjdpd0liVUFpckc1NWRpemNjWDZDczRKZzBKQjVfMnVOMEdKMTVhMzhKaDhEN3hXOGVyYjdfaWd6NmtpbDg?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Guia do Investidor</t>
+          <t>Acionista.com.br</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-18T15:21:11+00:00</t>
+          <t>2026-06-18T17:42:20+00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1024,19 +1024,19 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado. Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
+          <t>PASS3 with target price of R$33 and appreciation of 32%. PASS3 with target price of R$33 and appreciation of 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19T19:03:51</t>
+          <t>2026-06-19T20:03:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1046,37 +1046,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0da4ad0ad7a2</t>
+          <t>dcd8cc10981b</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%</t>
+          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE03RElkdzFzcUI2bl8wdkdLaVRveHhqMFlpb1ZlU3M1YVo0c29NMnQwZGRaRGZ0MTVmSno1eVlYbFpKVjdpd0liVUFpckc1NWRpemNjWDZDczRKZzBKQjVfMnVOMEdKMTVhMzhKaDhEN3hXOGVyYjdfaWd6NmtpbDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUmlwQU1FbFMyUTBfa1VTVG9fMkVFMlRGdXNqaW1kbnVqTjNhMmx6M1o5SHdwQV9FejBFWHp0eThoTC1pMVNVaHNCeVBaZlJBTkRTbDhmc19uNG9iQVItSXBmQUtQUFNvUnQ4Y19QNU92SnllR0Vmd0VMM2p2RUJORU9PRHpubXRYWEtTX2lNMkh1dGJWUEc2RUtYRHptVGdJQnZMS3V1T0dGdw?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acionista.com.br</t>
+          <t>Money Times</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-18T17:42:20+00:00</t>
+          <t>2026-06-18T15:21:00+00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1103,91 +1103,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%. PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Why can this Cosan company (CSAN3) be a dividend machine? Why this Cosan company (CSAN3) can be a dividend machine?&amp;nbsp;&amp;nbsp;Money Times</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>No module named 'transformers'</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-19T19:03:51</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PASS3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dcd8cc10981b</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUmlwQU1FbFMyUTBfa1VTVG9fMkVFMlRGdXNqaW1kbnVqTjNhMmx6M1o5SHdwQV9FejBFWHp0eThoTC1pMVNVaHNCeVBaZlJBTkRTbDhmc19uNG9iQVItSXBmQUtQUFNvUnQ4Y19QNU92SnllR0Vmd0VMM2p2RUJORU9PRHpubXRYWEtTX2lNMkh1dGJWUEc2RUtYRHptVGdJQnZMS3V1T0dGdw?oc=5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Money Times</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-06-18T15:21:00+00:00</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Comgás</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVO</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVO</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?. Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>No module named 'transformers'</t>
+          <t>string indices must be integers, not 'str'</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1145,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/relatorio_sentimentos.xlsx
+++ b/data/relatorio_sentimentos.xlsx
@@ -37,8 +37,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -495,46 +495,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.8689</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>POSITIVO</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,61 +641,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8437c62dc702</t>
+          <t>aa651ab08174</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO</t>
+          <t>Cosan (CSAN3) intensifica redução de dívida com R$ 2,8 bi em pré-pagamentos; total chega a R$ 8,8 bi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASS3 ganha aval de grandes bancos e pode subir até 52% após IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
+          <t>Cosan (CSAN3) intensifica redução de dívida com R$ 2,8 bi em pré-pagamentos; total chega a R$ 8,8 bi  Estadão</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPczBJd2hKQ2RwOHVlZzNNbTBFakJSMGNyalEtTFRQSnZYaThuUEcwdzFNWVJoMlBLUkgzQVRIRHEwSlpzay1paE02MzhhWVdfUUd0alR6RVRURnBUUHpBdS05ZDgzbXJPUmk1SHRyd0lDWFBvdnBKazZJaFczWTRNX0xOdDlFUmhTN3RKZ0EyMzVsbXlSZ1Exc1Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOYlNKeWpaV25tSUxmQ01iZVdTU05ESDk1WEM5Z3hlS09wV2dyMVJwTFRYMC1XWDZvZzJXdmpQNlB4MmZmU2hxeXBzdmFIdjc2RTR6cHE5ZVphMnNOQjc1cGNLZ2hVVWtoa3FqdUFDZ1UyOGZGeU5ybXZ4cWkwMndJQ2ktVEoxQ05BUS0wSW9BUURBVDU5SUxLbGpaZ2RQZXJ4YjRzdnNQWS1KSEN3RUFFeHFGeHhiWk41LWdabGVXcl8zbFBIUm1nU3pOU0pCNGg1aWhOalJPQ2NOWTFxMEI4cXZJMV9URGfSAewBQVVfeXFMTnozXzhoZDFraG9ZWHFNNk5jdzBPVzlVczkxelExWE1EdkdrUEJ2WnNyRUVRM0dHU3JfMUk0SnN2a1pJVXRCMWROUm1ad1RlcGppbDNYbzAyLUpnTFpuZUFFS19VX3BiZ1VmVlBTbUZocmZQd0g4SGZoaGctNWJsQ20xWTlVT2hUdnJQbmFWakM2YV90akVQS3pDSFpaTkdET3lreG0wTHVad1Zrem1zOWtWajhyTE9UXzhwekxEQmtLRUZLcDRkSjVFbHJTUnBnckM2cVVPcDlKQU1sS2RyTzFaMUFHQUpNS0MxdXo?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>arevista.com.br</t>
+          <t>Estadão</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19T16:30:29+00:00</t>
+          <t>2026-06-20T00:24:03+00:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>POSITIVO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.8208</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -708,73 +708,69 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PASS3 gains endorsement from large banks and could rise up to 52% after IPO. PASS3 gains endorsement from large banks and could rise up to 52% after IPO&amp;nbsp;&amp;nbsp;arevista.com.br</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+          <t>Cosan (CSAN3) intensifies debt reduction with R$2.8 billion in prepayments; total reaches R$8.8 billion. Cosan (CSAN3) intensifies debt reduction with R$2.8 billion in prepayments; total reaches R$ 8.8 billion Estadão</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>93e511b82050</t>
+          <t>cf17dde11773</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso</t>
+          <t>Sentimento virou? Por que os analistas estão ficando mais otimistas com Cosan (CSAN3)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
+          <t>Sentimento virou? Por que os analistas estão ficando mais otimistas com Cosan (CSAN3)  InfoMoney</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41WDkwUmlQeVRGYjNkLW5Lc3FpMFFUeVFxWVpCcjN2T0FXb0o4bEdBaDdTLTFTVjRkVnZKWFpFQ1FkUkFtaXFmbG12TTFldWczZ25JcW53N1A0M0U0MHRpZU0wS3lENzAzMW5VaGh6Y00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPeXRWLU5OVDREcktyNnNUOXZQM0ZnTHUzdHEzT3Jvclg3d2g3TDFuT3FpLVctZU5YLUgwcUtOOWgxR2R5LWVUTzQ0cDVQdllsUG5uSUtwWGVNR1F5VnRvU3lRT1ltUElWZkVONDhuQzJwckhlSll4akNXYWt2TWx4aTR6R0s5SGZGUmdRbDFGOTJOdkpHRFdvRjFzZ0dOd2NGSTVqUmlWdGd2Z2ZqMGRPS3IwUlZoaVhITDNsd3B30gHDAUFVX3lxTE5FM1BBd196UkhBYWdWazBJT05wZG4wWldST2J2eUNpdmpSdTJDYWdKRlpOOUMxTjVwOFI4eGFBeWcwTHNuX2RISDJ4SVFORWJDNWlzZmxvcE9HQVpLY0RrNjN5OGhweUtrOTl3aXc2aEJTaFRWb09YNG80RGhtdi1iTHBEWkpzYXZNaGRvN1BXYmVObmdfZXU0TXJLUFhJcG41Q1Q0VEQ5eHo3T1BuYXlEMmlRMDFIaVNRYTJWMlNhU01wVQ?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tradenews.com.br</t>
+          <t>InfoMoney</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-18T18:01:39+00:00</t>
+          <t>2026-06-19T16:27:11+00:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.8364</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -787,73 +783,69 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario. Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario&amp;nbsp;&amp;nbsp;tradenews.com.br</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+          <t>Feeling turned? Why analysts are becoming more optimistic about Cosan (CSAN3). Feeling turned? Why analysts are becoming more optimistic about Cosan (CSAN3) InfoMoney</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6501afb16592</t>
+          <t>561beeaea53e</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PASS3 projeta valorização superior a 50% com recomendações de compra</t>
+          <t>Cosan (CSAN3): Bradesco BBI corta preço-alvo, mas juros menores e venda de ativos podem destravar valor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PASS3 projeta valorização superior a 50% com recomendações de compra&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Cosan (CSAN3): Bradesco BBI corta preço-alvo, mas juros menores e venda de ativos podem destravar valor  Money Times</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPeXpHT21BQjJxLTlMeGhGQVF0WHRSMHpVanhJTFRuVE9Zdk9VeGtPZlV5TmZoRFp1Z185WDY3dWZ2X1ZxY2FYejllRGVwY3VWaWNOZzN4eTJYc3dPcm9teGVMOVl0dGJaczNVLWZaejJhR3dKU2V2cXVVU3dLdFhUQWNTcTlfa0Jab2I5S2F6OU9KbjFMVXIySw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPc205QVVUWHQ3c1JyUWljb0RPN213b00zZlFYaUFpTW9JUk1IT1I1RUxHWFpkOTl4VjZWUGxjdVl6UkNfRDN6TEVTTXl6YWtMOGZrY0tab0dZbmFpVTZxQktoLTI5UEFMRjFpdS1PZzdwUGZXeG9aaGg1a1RvZnd1dmVPblFlcUtFajN5VTA0XzJIcTZ6VzJtZkNIWFR3am52Wk9JclVwaFU2cGFWR1R1ZEpQSjZuenVoeGc0aVdkRkpGcS1lcGdxSVloOXlWSzJf?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acionista.com.br</t>
+          <t>Money Times</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-18T10:44:36+00:00</t>
+          <t>2026-06-19T14:29:00+00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>POSITIVO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.874</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -866,73 +858,69 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PASS3 projects appreciation of more than 50% with purchase recommendations. PASS3 projects appreciation of more than 50% with purchase recommendations&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+          <t>Cosan (CSAN3): Bradesco BBI cuts target price, but lower interest rates and asset sales could unlock value. Cosan (CSAN3): Bradesco BBI cuts target price, but lower interest rates and asset sales could unlock value Money Times</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15a530bd9989</t>
+          <t>fbaa42ddd0f2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado</t>
+          <t>Cosan (CSAN3) acelera redução da dívida e conclui pré-pagamentos de R$ 2,8 bilhões</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Compass (PASS3): cinco bancos veem alta de até 49% e apontam erro do mercado&amp;nbsp;&amp;nbsp;Guia do Investidor</t>
+          <t>Cosan (CSAN3) acelera redução da dívida e conclui pré-pagamentos de R$ 2,8 bilhões  Seu Dinheiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPY2hTVGduakFZNUZxamFhcWFXUFZZUm5JSkVwQW5ESmRkSkhnRTkwNWItelJrbmt0a09DUmFBTEZnNllZTHVZaHVkNXo3RHN5clduQi1zUFI5M19Sby1FeHIwUVlSa3pUbTlfa0prMUJ4ZFhfclBOUy16cF9FV0xxbjJSaHlmVmkyYWdYTjd6TDhvTGdlN1FZZ1JVOGJsRjJ5NjlKVk5uekdNS0hzeVVyd3YzRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNbDVoeXJmazZvclFteFRad09PUkNld2hiMGhkdlB5X2pYc2ExQzlIQkZPUUNhQVVZajk5RnF4REZGdERUVmVhNFRVVXFkMkpRLTBtemRrZDNNU2VQamdNdWo5ZFZWVGFYZnFyUmIyVmNnN3hWeU5aR2h4aVNya0dHU1lPUENjTFJXdC1WX2FJMmJXT05vN0tLLV9ZYmVjRWZ3VjJZSm9IVktiQW9oeE5KOVoySTIxREp1ZmlMdzFLLXRwWmthZHRR?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Guia do Investidor</t>
+          <t>Seu Dinheiro</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-18T15:21:11+00:00</t>
+          <t>2026-06-19T22:32:34+00:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>POSITIVO</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.884</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -945,73 +933,69 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Compass (PASS3): five banks see an increase of up to 49% and point out a market error. Compass (PASS3): five banks see an increase of up to 49% and point out market error&amp;nbsp;&amp;nbsp;Investor Guide</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+          <t>Cosan (CSAN3) accelerates debt reduction and completes prepayments of R$2.8 billion. Cosan (CSAN3) accelerates debt reduction and completes prepayments of R$2.8 billion Your Money</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0da4ad0ad7a2</t>
+          <t>0db4444649c9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%</t>
+          <t>Cosan (CSAN3) anuncia conclusão de pré-pagamentos de R$ 2,8 bi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PASS3 com preço-alvo de R$ 33 e valorização de 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
+          <t>Cosan (CSAN3) anuncia conclusão de pré-pagamentos de R$ 2,8 bi  financenews.com.br</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE03RElkdzFzcUI2bl8wdkdLaVRveHhqMFlpb1ZlU3M1YVo0c29NMnQwZGRaRGZ0MTVmSno1eVlYbFpKVjdpd0liVUFpckc1NWRpemNjWDZDczRKZzBKQjVfMnVOMEdKMTVhMzhKaDhEN3hXOGVyYjdfaWd6NmtpbDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPdVlMbGZTbjFYU3lLY2NTMU5KMGk1SklmWGhNV01LMnh1anRMeGJMazU4ZE1GRDhfNDhfbmxBY191Q2NuQkVFSUtPOGdoME5VaDhLSlZYcTlmYm1wbnJsYktIdEFZRWhrbmRpTVN6Rm5yOFRkbUFjYmM1SVk4a3FyS2NBbXZ2TGUtS1d6aEQzMVo5NE9CRE9JMDVn?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acionista.com.br</t>
+          <t>financenews.com.br</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-18T17:42:20+00:00</t>
+          <t>2026-06-20T23:35:39+00:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.8704</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1024,93 +1008,160 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PASS3 with target price of R$33 and appreciation of 32%. PASS3 with target price of R$33 and appreciation of 32%&amp;nbsp;&amp;nbsp;Acionista.com.br</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+          <t>Cosan (CSAN3) announces completion of prepayments of R$2.8 billion. Cosan (CSAN3) announces completion of prepayments of R$ 2.8 billion financenews.com.br</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19T20:03:54</t>
+          <t>2026-06-21T10:58:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dcd8cc10981b</t>
+          <t>0d4e66774df2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?</t>
+          <t>Cosan (CSAN3) conclui pré-pagamentos de R$ 2,8 bi e reduz dívida em R$ 8,8 bi no ano</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Por que esta empresa da Cosan (CSAN3) pode ser uma máquina de dividendos?&amp;nbsp;&amp;nbsp;Money Times</t>
+          <t>Cosan (CSAN3) conclui pré-pagamentos de R$ 2,8 bi e reduz dívida em R$ 8,8 bi no ano  Investidor10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUmlwQU1FbFMyUTBfa1VTVG9fMkVFMlRGdXNqaW1kbnVqTjNhMmx6M1o5SHdwQV9FejBFWHp0eThoTC1pMVNVaHNCeVBaZlJBTkRTbDhmc19uNG9iQVItSXBmQUtQUFNvUnQ4Y19QNU92SnllR0Vmd0VMM2p2RUJORU9PRHpubXRYWEtTX2lNMkh1dGJWUEc2RUtYRHptVGdJQnZMS3V1T0dGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNNGpaQm9aQVoyYk9wSlNyNlgyRGEyeUVzeTY3N3ZtOWdtMTc4WWRQVE5wOXA5UF9ZQmJ3ZXdBOTNCZDJzVVkwVURQN21MX1JRejRZODdpZVhGN1BCRnFGbjc0MjVZV2U4OHNaUzBLRGdhbHg1cE4wcWhnRDZIVW16Q29wcFdoellwdEpJQk9ka002alJveVV0anl3bWFoWFVGcG8zMTFBS3pYN2N0b3l0UV9JbG93TXc1d01DbzktbFdmQmNiRlpNS9IByAFBVV95cUxNNGpaQm9aQVoyYk9wSlNyNlgyRGEyeUVzeTY3N3ZtOWdtMTc4WWRQVE5wOXA5UF9ZQmJ3ZXdBOTNCZDJzVVkwVURQN21MX1JRejRZODdpZVhGN1BCRnFGbjc0MjVZV2U4OHNaUzBLRGdhbHg1cE4wcWhnRDZIVW16Q29wcFdoellwdEpJQk9ka002alJveVV0anl3bWFoWFVGcG8zMTFBS3pYN2N0b3l0UV9JbG93TXc1d01DbzktbFdmQmNiRlpNSw?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Investidor10</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CSAN3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cosan (CSAN3) completes prepayments of R$2.8 billion and reduces debt by R$8.8 billion in the year. Cosan (CSAN3) completes prepayments of R$2.8 billion and reduces debt by R$8.8 billion in the year Investor10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-21T10:58:31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSAN3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>de2bb2f1f29c</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cosan (CSAN3) conclui pré-pagamentos de R$ 2,8 bilhões e avança na redução da dívida</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cosan (CSAN3) conclui pré-pagamentos de R$ 2,8 bilhões e avança na redução da dívida  Money Times</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPMldCMU53ZjU1NmZvZ0dnQkZCYUljWmJlVnlJTkMwODlqNmZmV0dNYTF3WjY3eU16ckszNjgyV2VvYU1ZUy1KZGV2X2V3Q002Ui1TbTl2aUhicmdxdTk1VHppS3VQZC1rUzd5dU5OSFp0VzRfMTJLNk5WRmhTOXRSM3A3OFJmd2s1RTh5RnI1bWY5bEhHRmY4TUFmMGFWME5BbmpoRGpick1tNFFrTld2dQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Money Times</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-06-18T15:21:00+00:00</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Comgás</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVO</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVO</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Why can this Cosan company (CSAN3) be a dividend machine? Why this Cosan company (CSAN3) can be a dividend machine?&amp;nbsp;&amp;nbsp;Money Times</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>string indices must be integers, not 'str'</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:46:00+00:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CSAN3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Cosan (CSAN3) completes prepayments of R$2.8 billion and advances in debt reduction. Cosan (CSAN3) completes prepayments of R$2.8 billion and advances in debt reduction Money Times</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,18 +1185,26 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>INCONCLUSIVO</t>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PASS3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/relatorio_sentimentos.xlsx
+++ b/data/relatorio_sentimentos.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>PASS3</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8689</v>
+        <v>0.9523</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>57.1</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,531 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>a2f432f4f7e7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Citi, JPMorgan e Itaú BBA iniciam cobertura da Compass (PASS3) com recomendação de compra  Estadão</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVENxdTl1SGIyb0VaeU1CT3VyTlRHNGZXdk56Smt3S1pPaXZOTmVFSi12Z295aTZQLUxNYmpFSmNHVFBxOE12ejlOT2VqU1BoR0ZhTTJPVTN3YUVxcFlkVmlDX0xPR2Q0RWQ3bzhuUWlFWFU0U2hxaVBZVHhXTnRPaFplUUtmVm5uMDJlSFJxR0FYM3hMSUJrRzdKN3ktSkg1NnZUekc1VHJfbDZlUkN0Wi1YaWUySlJVZkI5LVl4NDBmdUkwYm9ZMXRDQjFYVUJaamdQZ3llc1haQ1V0akHSAeMBQVVfeXFMTjNnR2lnMFB2NmFoXzBRMEVlWFpHZ3BYamIzbXpVMXpORlZrRVJhdndCQ0lXcjNtVGlDakpSWmlhR1A3SENaSndBRXNFeU85SkV1TEZ5M0MwZVBOWnhsWl9nWmU2Y2k0RXdySVBjZFhfODdGRW9RUGtJRWlwTjVkak9vN1RQaC1Gek1JYVJVRUJTRGVrU0ZlSFYwMktTX29oc19rZFY0M1hfUE1YLUtHTjBhN3hTMlVnRm9SRE51X0VNZlM4QktEZmY0M2h2a2tsSFZnUU1EQ2htcmpUbTBaY05rcWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Estadão</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-17T22:39:45+00:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9315</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Citi, JPMorgan and Itaú BBA begin coverage of Compass (PASS3) with a buy recommendation. Citi, JPMorgan and Itaú BBA begin coverage of Compass (PASS3) with purchase recommendation Estadão</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ff5aa0aa6a4a</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Compass (PASS3): 4 bancos iniciam cobertura recomendando compra e ação sobe forte</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Compass (PASS3): 4 bancos iniciam cobertura recomendando compra e ação sobe forte  InfoMoney</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTUhUNEM4QWF5YmdISlVnNTJ6T0RadmtONnNvRDVmbGs3dkdkN0F3eWhPR1pMQ0EtQXQxdXItYzZZeUNESUxLVEZ3dlZwZWJ0VFZPQkExM0MwYVRpbkhKNV9Jc2F4QmNHdEZmTjdfczVwb0N3djNiQmdpcEhFT0w5V285VmRmWVQ3NU1tcHFkaE51Sk9wbTFYRmlPMW9oM250N0FRSS1YSnp6NHVaXzExZ0czT1J3YkVG0gG-AUFVX3lxTFBEd25taFhTMTBoa3hyNzNVR3VwYkFXMFFYdVgtYnVPeWllLWVlVTZIYVdDYVdiNkdneDAta2FXazVQSDVFZ1p3bFQycFA3TmFBbmZqQXNnaFBwWUdWVUVCVy11SlFjMVJJT2lBcmQycmRnSVp2Rm1UT3piVFpVenFteXNKN0p0UjZ6Z21pX0k2NHNyejJSTVFaUjNaSV9nc1V1eTk3MmtxV285N1J1aHZHa21MaE1FVlcyQnRJMlE?oc=5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>InfoMoney</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-06-17T13:57:37+00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Compass (PASS3): 4 banks begin coverage recommending purchase and the stock rises sharply. Compass (PASS3): 4 banks begin coverage recommending purchase and share rises sharply InfoMoney</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>671b9d2848bc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) virou a nova aposta da Faria Lima? Ação conquista selo de compra de três bancões — e potencial de alta passa dos 50%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) virou a nova aposta da Faria Lima? Ação conquista selo de compra de três bancões — e potencial de alta passa dos 50%  Seu Dinheiro</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPUkdaeGxBbVNMQmtGbE51dUNVc3dVTnRDWEdKa09CNmJ0SjQtX2oxcFFDb1pUNmpjMkw1SS1hMDZYRV9GRVltcmtQelQzcGVZaHRrSWJYQ3ltMzRrQ1Y4bmFna0dQb1l2ZEJYYUxPR3IxOUE3SzdvQWQ0OVRDZ2s1MWI4T250M3d6Xy1na21mXzNfcGFNdEdLRjdjdDZwdTdfS24xZVB4V2xuU1R2QUJPSjhmU1dXc2phSm9HMl9XZTNuU0JRVTJNcEJTQ1cwZ1ZITE5FeDl5VzRGM2FOdUNYRk5sMXQtclBmM0JVTjFzR1J1cGhTTXA3dGt0VDdWMnZVbXFUUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Seu Dinheiro</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-17T15:53:18+00:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.9679</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) has become Faria Lima's new bet? Action wins purchase seal from three banks — and potential increase exceeds 50%. Compass (PASS3) has become Faria Lima's new bet? Action wins purchase seal from three banks — and potential upside exceeds 50% Your Money</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>a4d6124a9fa1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) pagará R$ 405,5 milhões em dividendos neste mês; veja quem tem direito</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) pagará R$ 405,5 milhões em dividendos neste mês; veja quem tem direito  Money Times</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNNU9Qbm42Nkl0VTYyWl9zZTc5Q0NhamJBcjE2Z21ROVQ4OWpWdjBEMWhYME42d2FCWG0yVHVkcnNwLWpuYVRiSENsLV9LX05xaVdtZEsxWU9zRHpNSVBCOXhuV2hZRVRIRXlPeC1SUElfX2VwOG9QSWhsQmhXTkdkX2pCOHN4UFdDQ0VaM1laQjM1UTNLZ0FiQ2QxRVJXMUF6bUpyMlFzSkRvczRDdGFSZVVKa2UyYmh1?oc=5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Money Times</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-06-16T11:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) will pay R$405.5 million in dividends this month; see who is entitled. Compass (PASS3) will pay R$405.5 million in dividends this month; see who is entitled Money Times</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>93e511b82050</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Compass [PASS3]: a joia da coroa da Cosan que resiste ao cenário macro adverso  tradenews.com.br</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41WDkwUmlQeVRGYjNkLW5Lc3FpMFFUeVFxWVpCcjN2T0FXb0o4bEdBaDdTLTFTVjRkVnZKWFpFQ1FkUkFtaXFmbG12TTFldWczZ25JcW53N1A0M0U0MHRpZU0wS3lENzAzMW5VaGh6Y00?oc=5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tradenews.com.br</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-06-18T18:01:39+00:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario. Compass [PASS3]: Cosan's crown jewel that resists the adverse macro scenario tradenews.com.br</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9334c1bbfddd</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) ganha selo de compra de BTG, Itaú BBA e Citi com potencial de alta acima de 50%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) ganha selo de compra de BTG, Itaú BBA e Citi com potencial de alta acima de 50%  BPMoney</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNjQyMVpGQXBrZG5tMnJVdXRPUk5ZX3g2dHZpV0FISENob1FXZEZZSXdjTU5UN01sQ0d2TjVkWEdfelZPalFSX28zQVpoYlk5VU1oYmVxcFkxZWxSejNNcHg4REtKZFRPTFdlY05qNXo4VVBaamgza3pLWGtNdVF1WFMxaWU4ZklmUDlldkg5bUNxam1PZTIySm5GMk0?oc=5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BPMoney</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-06-17T17:15:06+00:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>POSITIVO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Compass (PASS3) receives a purchase seal from BTG, Itaú BBA and Citi with potential for an increase of over 50%. Compass (PASS3) gains purchase seal from BTG, Itaú BBA and Citi with upside potential of over 50% BPMoney</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-21T11:08:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3f14dfc195cf</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Compass Gás e Energia (PASS3) pagará em 29 de junho dividendo aprovado em abril</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Compass Gás e Energia (PASS3) pagará em 29 de junho dividendo aprovado em abril  financenews.com.br</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPUE55NTJKMWtWbFdGMDJhbUI4NnNwXzFkYTdUTEY0YnBXWEZLMERMckZhSXIzVTAtRnVzd3dmci03cTlLNUx4M1BlRXpxY3JyeTNsOTdXS0xDYUVVTlRmWWlrbC0tX1BiUTVCVldFdjA5MnVMdWdpbFM5X09BZmZSc296MGpVTjVYbE5JTXU0RWFaMm9ZYVJGSXFWNTB2SXNJYUl2TEctaWp1OUVlVEUxSEI1bw?oc=5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>financenews.com.br</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-06-16T00:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9442</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Compass Gás e Energia (PASS3) will pay a dividend approved in April on June 29th. Compass Gás e Energia (PASS3) will pay dividends approved in April on June 29th financenews.com.br</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1174,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,6 +1732,19 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PASS3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
